--- a/artfynd/A 2256-2025 artfynd.xlsx
+++ b/artfynd/A 2256-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99676998</v>
+        <v>104657307</v>
       </c>
       <c r="B2" t="n">
-        <v>57246</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100130</v>
+        <v>164</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buskmus</t>
+          <t>Nordlåsbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sicista betulina</t>
+          <t>Botrychium boreale</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1779)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>fälla</t>
+          <t>Milde</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillviken, Pi lm</t>
+          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549099.8346131126</v>
+        <v>550076</v>
       </c>
       <c r="R2" t="n">
-        <v>7396056.031229308</v>
+        <v>7394750</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,58 +769,53 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jeroen van der Kooij</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jeroen van der Kooij, Pavel Bina</t>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av buskmus</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104657299</v>
+        <v>104657309</v>
       </c>
       <c r="B3" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98049</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>164</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nordlåsbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Botrychium boreale</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Milde</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,14 +825,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553183.5512070502</v>
+        <v>551384</v>
       </c>
       <c r="R3" t="n">
-        <v>7391496.287260138</v>
+        <v>7393787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,19 +862,9 @@
           <t>2022-07-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,59 +895,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104657307</v>
+        <v>2552228</v>
       </c>
       <c r="B4" t="n">
-        <v>96687</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99049</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>164</v>
+        <v>219794</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordlåsbräken</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Botrychium boreale</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Milde</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
+          <t>Mierkenis, strax O om, artrik vägslänt, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550076</v>
+        <v>549441</v>
       </c>
       <c r="R4" t="n">
-        <v>7394750</v>
+        <v>7395630</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,12 +960,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,35 +976,35 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>artrik vägslänt</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Charlotte Nordgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Charlotte Nordgren, Mats G Nettelbladt, Maj-Lis Granström, Ann-mari Sundkvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104657301</v>
+        <v>2634889</v>
       </c>
       <c r="B5" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,43 +1012,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222424</v>
+        <v>219795</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällummer</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium alpinum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Mierkenis, strax O om, artrik vägslänt, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553177.4136022304</v>
+        <v>549441</v>
       </c>
       <c r="R5" t="n">
-        <v>7391505.304085981</v>
+        <v>7395630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,22 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,35 +1082,35 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>artrik vägslänt</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Charlotte Nordgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Charlotte Nordgren, Mats G Nettelbladt, Maj-Lis Granström, Ann-mari Sundkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104657300</v>
+        <v>2463890</v>
       </c>
       <c r="B6" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,43 +1118,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222424</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium alpinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Mierkenis, strax O om, artrik vägslänt, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553178.5906542003</v>
+        <v>549441</v>
       </c>
       <c r="R6" t="n">
-        <v>7391506.121103835</v>
+        <v>7395630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,22 +1172,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,35 +1188,35 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>artrik vägslänt</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Charlotte Nordgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Charlotte Nordgren, Maj-Lis Granström, Mats G Nettelbladt, Ann-mari Sundkvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104657309</v>
+        <v>104657310</v>
       </c>
       <c r="B7" t="n">
-        <v>96687</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,26 +1224,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>164</v>
+        <v>222112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordlåsbräken</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Botrychium boreale</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Milde</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1335,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551384</v>
+        <v>550173</v>
       </c>
       <c r="R7" t="n">
-        <v>7393787</v>
+        <v>7394559</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1401,15 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104657315</v>
+        <v>104657311</v>
       </c>
       <c r="B8" t="n">
-        <v>96688</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1353,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1450,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550096</v>
+        <v>550097</v>
       </c>
       <c r="R8" t="n">
-        <v>7394713</v>
+        <v>7394684</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,42 +1433,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104657302</v>
+        <v>104657313</v>
       </c>
       <c r="B9" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222424</v>
+        <v>222112</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällummer</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium alpinum</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1561,14 +1473,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553179.5384795179</v>
+        <v>550060</v>
       </c>
       <c r="R9" t="n">
-        <v>7391498.195854648</v>
+        <v>7394762</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1598,19 +1510,9 @@
           <t>2022-07-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1641,54 +1543,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80435343</v>
+        <v>104657314</v>
       </c>
       <c r="B10" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>222112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väg 95, 2 km V Sandviken, Pi lm</t>
+          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552990.6270587323</v>
+        <v>550085</v>
       </c>
       <c r="R10" t="n">
-        <v>7391873.840299418</v>
+        <v>7394709</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1715,22 +1617,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-06-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,69 +1631,76 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson, Börje Törnberg</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2463889</v>
+        <v>104657315</v>
       </c>
       <c r="B11" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>222112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandviken, strax V om, artrik vägslänt, Pi lm</t>
+          <t>Sandviken-Merkemsvupmekitje Skårrim, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553683.5804163999</v>
+        <v>550096</v>
       </c>
       <c r="R11" t="n">
-        <v>7390562.903086151</v>
+        <v>7394713</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,22 +1727,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,40 +1743,30 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>artrik vägslänt</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren, Mats G Nettelbladt, Maj-Lis Granström, Ann-mari Sundkvist</t>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104657319</v>
+        <v>5988013</v>
       </c>
       <c r="B12" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,43 +1774,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>223597</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Mierkenis, strax O om, artrik vägslänt, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555154.6253099004</v>
+        <v>549441</v>
       </c>
       <c r="R12" t="n">
-        <v>7389117.441668341</v>
+        <v>7395630</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1958,22 +1824,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,82 +1840,84 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>artrik vägslänt</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Charlotte Nordgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Charlotte Nordgren, Mats G Nettelbladt, Maj-Lis Granström, Ann-mari Sundkvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104657320</v>
+        <v>102038448</v>
       </c>
       <c r="B13" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57791</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219811</v>
+        <v>102620</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Sandviken 965, Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555289.0103356413</v>
+        <v>552520</v>
       </c>
       <c r="R13" t="n">
-        <v>7387630.580015692</v>
+        <v>7392505</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2083,22 +1941,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2022-07-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
+          <t>2022-07-03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2113,31 +1971,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104657304</v>
+        <v>80435343</v>
       </c>
       <c r="B14" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,43 +1994,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vouggatjålme, Pi lm</t>
+          <t>Väg 95, 2 km V Sandviken, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555301.3321170842</v>
+        <v>552991</v>
       </c>
       <c r="R14" t="n">
-        <v>7387611.734607426</v>
+        <v>7391874</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,22 +2052,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2232,37 +2066,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Elisabet Arvidson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2634914</v>
+        <v>104657299</v>
       </c>
       <c r="B15" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,37 +2096,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219795</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vuoggatjålmejaure mellan väg 95 och kraftledningen, Pi lm</t>
+          <t>Vouggatjålme, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558709.358687592</v>
+        <v>553184</v>
       </c>
       <c r="R15" t="n">
-        <v>7383327.088715666</v>
+        <v>7391496</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2324,22 +2159,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,40 +2175,30 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>extremrikkärr</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4400318</v>
+        <v>2463889</v>
       </c>
       <c r="B16" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,37 +2206,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vuoggatjålmejaure mellan väg 95 och kraftledningen, Pi lm</t>
+          <t>Sandviken, strax V om, artrik vägslänt, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558709.358687592</v>
+        <v>553684</v>
       </c>
       <c r="R16" t="n">
-        <v>7383327.088715666</v>
+        <v>7390563</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2445,22 +2260,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2474,7 +2279,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>extremrikkärr</t>
+          <t>artrik vägslänt</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2485,10 +2290,1640 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
+          <t>Charlotte Nordgren, Mats G Nettelbladt, Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104657300</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97982</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222424</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fjällummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium alpinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>553178</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7391506</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104657301</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97982</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222424</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fjällummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium alpinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>553177</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7391505</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104657302</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97982</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222424</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium alpinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>553180</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7391498</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104657317</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>555155</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7389117</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2552215</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99049</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219794</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sumpnycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sandviken, Silvervägen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>554698</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7389785</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2012-07-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2012-07-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>104657296</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>555305</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7387598</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>104657298</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>555105</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7388477</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>104657304</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>555301</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7387612</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>104657320</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>555289</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7387631</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2463597</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sandviken, Silvervägen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>554380</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7389914</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2012-07-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2012-07-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>104657293</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>555298</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7387615</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>104657321</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vouggatjålme, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>554581</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7389832</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2634914</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vuoggatjålmejaure mellan väg 95 och kraftledningen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>558709</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7383327</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>extremrikkärr</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Charlotte Nordgren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
           <t>Charlotte Nordgren, Mats G Nettelbladt</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr">
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>4400318</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Vuoggatjålmejaure mellan väg 95 och kraftledningen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>558709</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7383327</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2012-07-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>extremrikkärr</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Charlotte Nordgren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>4898865</v>
+      </c>
+      <c r="B31" t="n">
+        <v>100143</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vuoggatjålmjaure SV, Tjålmevaratj S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>558757</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7383211</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2012-07-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2012-07-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>sluttningsmyr</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mats G Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mats G Nettelbladt, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
         <is>
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>

--- a/artfynd/A 2256-2025 artfynd.xlsx
+++ b/artfynd/A 2256-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657307</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2552228</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2634889</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2463890</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657310</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657311</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1430,6 +1465,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657313</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657314</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657315</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5988013</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135107148</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657299</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2074,6 +2139,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2463889</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2184,6 +2254,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657300</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2294,6 +2369,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657301</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2404,6 +2484,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657302</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2514,6 +2599,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657309</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2632,6 +2722,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102038448</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2734,6 +2829,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80435343</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2844,6 +2944,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657317</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2950,6 +3055,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2552215</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3060,6 +3170,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657296</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3170,6 +3285,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657298</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3280,6 +3400,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657304</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3390,6 +3515,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657320</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3496,6 +3626,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2463597</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3606,6 +3741,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657293</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3716,6 +3856,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657321</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3822,6 +3967,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2634914</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3928,6 +4078,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4400318</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4034,8 +4189,46 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4898865</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 2256-2025 artfynd.xlsx
+++ b/artfynd/A 2256-2025 artfynd.xlsx
@@ -1813,7 +1813,7 @@
         <v>135107148</v>
       </c>
       <c r="B12" t="n">
-        <v>99115</v>
+        <v>99162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2256-2025 artfynd.xlsx
+++ b/artfynd/A 2256-2025 artfynd.xlsx
@@ -1813,7 +1813,7 @@
         <v>135107148</v>
       </c>
       <c r="B12" t="n">
-        <v>99162</v>
+        <v>99189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
